--- a/Data/EC/NIT-9006463224.xlsx
+++ b/Data/EC/NIT-9006463224.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C453DAD0-5CC3-43FF-A738-E8F88104C3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{571CF848-F801-473E-A382-FD984C1B7074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{05D49485-53C2-4D28-9E4B-F67059C1EC14}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4F9E9DB1-4646-4074-9FBC-137204289677}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -71,6 +71,165 @@
     <t>YANIRIS BARRERA ROJAS</t>
   </si>
   <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
+    <t>1705</t>
+  </si>
+  <si>
+    <t>1704</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>1701</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
     <t>1609</t>
   </si>
   <si>
@@ -78,165 +237,6 @@
   </si>
   <si>
     <t>JULIO CESAR VALDERRAMA RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>1611</t>
-  </si>
-  <si>
-    <t>1612</t>
-  </si>
-  <si>
-    <t>1701</t>
-  </si>
-  <si>
-    <t>1702</t>
-  </si>
-  <si>
-    <t>1703</t>
-  </si>
-  <si>
-    <t>1704</t>
-  </si>
-  <si>
-    <t>1705</t>
-  </si>
-  <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2102</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -335,159 +335,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
       </top>
       <bottom style="thin">
         <color indexed="64"/>
@@ -505,6 +355,156 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -550,23 +550,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -594,10 +594,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -635,22 +635,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F9F58F7-FDDC-DD47-BBDB-CDE6D23C5CFD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B8E56B6-8725-BCBC-8E0B-BE2E3896F5B9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -672,7 +672,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1001,23 +1001,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CAF67EB-062A-403D-A7A5-385ECDBC4DB1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04BA1DCA-A681-4805-80FD-3F17C218D0CF}">
   <dimension ref="B2:J84"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1030,7 +1030,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1041,7 +1041,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1052,7 +1052,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1063,8 +1063,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>68</v>
       </c>
@@ -1079,8 +1079,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1095,8 +1095,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>69</v>
       </c>
@@ -1111,8 +1111,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>70</v>
       </c>
@@ -1131,7 +1131,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>27578</v>
+        <v>22916</v>
       </c>
       <c r="G16" s="18">
         <v>781242</v>
@@ -1183,21 +1183,21 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>11</v>
-      </c>
       <c r="F17" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G17" s="18">
         <v>781242</v>
@@ -1206,7 +1206,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1217,10 +1217,10 @@
         <v>10</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F18" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G18" s="18">
         <v>781242</v>
@@ -1229,21 +1229,21 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G19" s="18">
         <v>781242</v>
@@ -1252,7 +1252,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G20" s="18">
         <v>781242</v>
@@ -1275,21 +1275,21 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G21" s="18">
         <v>781242</v>
@@ -1298,7 +1298,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1309,10 +1309,10 @@
         <v>10</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F22" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G22" s="18">
         <v>781242</v>
@@ -1321,21 +1321,21 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F23" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G23" s="18">
         <v>781242</v>
@@ -1344,7 +1344,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1355,10 +1355,10 @@
         <v>10</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F24" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G24" s="18">
         <v>781242</v>
@@ -1367,21 +1367,21 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F25" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G25" s="18">
         <v>781242</v>
@@ -1390,7 +1390,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1401,10 +1401,10 @@
         <v>10</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F26" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G26" s="18">
         <v>781242</v>
@@ -1413,21 +1413,21 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F27" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G27" s="18">
         <v>781242</v>
@@ -1436,7 +1436,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1447,10 +1447,10 @@
         <v>10</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F28" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G28" s="18">
         <v>781242</v>
@@ -1459,7 +1459,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1470,10 +1470,10 @@
         <v>10</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F29" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G29" s="18">
         <v>781242</v>
@@ -1482,21 +1482,21 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F30" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G30" s="18">
         <v>781242</v>
@@ -1505,7 +1505,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1516,10 +1516,10 @@
         <v>10</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F31" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G31" s="18">
         <v>781242</v>
@@ -1528,21 +1528,21 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F32" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G32" s="18">
         <v>781242</v>
@@ -1551,7 +1551,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1562,10 +1562,10 @@
         <v>10</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F33" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G33" s="18">
         <v>781242</v>
@@ -1574,21 +1574,21 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F34" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G34" s="18">
         <v>781242</v>
@@ -1597,7 +1597,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1608,10 +1608,10 @@
         <v>10</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F35" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G35" s="18">
         <v>781242</v>
@@ -1620,7 +1620,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1631,10 +1631,10 @@
         <v>10</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F36" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G36" s="18">
         <v>781242</v>
@@ -1643,7 +1643,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1654,10 +1654,10 @@
         <v>10</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F37" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G37" s="18">
         <v>781242</v>
@@ -1666,7 +1666,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1677,10 +1677,10 @@
         <v>10</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F38" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G38" s="18">
         <v>781242</v>
@@ -1689,7 +1689,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1700,10 +1700,10 @@
         <v>10</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F39" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G39" s="18">
         <v>781242</v>
@@ -1712,7 +1712,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1723,10 +1723,10 @@
         <v>10</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F40" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G40" s="18">
         <v>781242</v>
@@ -1735,7 +1735,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1746,10 +1746,10 @@
         <v>10</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F41" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G41" s="18">
         <v>781242</v>
@@ -1758,7 +1758,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1769,10 +1769,10 @@
         <v>10</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F42" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G42" s="18">
         <v>781242</v>
@@ -1781,7 +1781,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1792,10 +1792,10 @@
         <v>10</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F43" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G43" s="18">
         <v>781242</v>
@@ -1804,7 +1804,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1815,10 +1815,10 @@
         <v>10</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F44" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G44" s="18">
         <v>781242</v>
@@ -1827,7 +1827,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1838,10 +1838,10 @@
         <v>10</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F45" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G45" s="18">
         <v>781242</v>
@@ -1850,7 +1850,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>10</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F46" s="18">
         <v>27578</v>
@@ -1873,7 +1873,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>10</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F47" s="18">
         <v>27578</v>
@@ -1896,7 +1896,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>10</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F48" s="18">
         <v>27578</v>
@@ -1919,7 +1919,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1930,10 +1930,10 @@
         <v>10</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F49" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G49" s="18">
         <v>781242</v>
@@ -1942,7 +1942,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1953,10 +1953,10 @@
         <v>10</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F50" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G50" s="18">
         <v>781242</v>
@@ -1965,7 +1965,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -1976,10 +1976,10 @@
         <v>10</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F51" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G51" s="18">
         <v>781242</v>
@@ -1988,7 +1988,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -1999,10 +1999,10 @@
         <v>10</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F52" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G52" s="18">
         <v>781242</v>
@@ -2011,7 +2011,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2022,10 +2022,10 @@
         <v>10</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F53" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G53" s="18">
         <v>781242</v>
@@ -2034,7 +2034,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2045,10 +2045,10 @@
         <v>10</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F54" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G54" s="18">
         <v>781242</v>
@@ -2057,7 +2057,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2068,10 +2068,10 @@
         <v>10</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F55" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G55" s="18">
         <v>781242</v>
@@ -2080,7 +2080,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2091,10 +2091,10 @@
         <v>10</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F56" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G56" s="18">
         <v>781242</v>
@@ -2103,7 +2103,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2114,10 +2114,10 @@
         <v>10</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F57" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G57" s="18">
         <v>781242</v>
@@ -2126,7 +2126,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2137,10 +2137,10 @@
         <v>10</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F58" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G58" s="18">
         <v>781242</v>
@@ -2149,7 +2149,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2160,10 +2160,10 @@
         <v>10</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F59" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G59" s="18">
         <v>781242</v>
@@ -2172,7 +2172,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2183,10 +2183,10 @@
         <v>10</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F60" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G60" s="18">
         <v>781242</v>
@@ -2195,7 +2195,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2206,10 +2206,10 @@
         <v>10</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F61" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G61" s="18">
         <v>781242</v>
@@ -2218,7 +2218,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2229,10 +2229,10 @@
         <v>10</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F62" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G62" s="18">
         <v>781242</v>
@@ -2241,7 +2241,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2252,10 +2252,10 @@
         <v>10</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F63" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G63" s="18">
         <v>781242</v>
@@ -2264,7 +2264,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2275,10 +2275,10 @@
         <v>10</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F64" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G64" s="18">
         <v>781242</v>
@@ -2287,7 +2287,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2298,10 +2298,10 @@
         <v>10</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F65" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G65" s="18">
         <v>781242</v>
@@ -2310,7 +2310,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2321,10 +2321,10 @@
         <v>10</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F66" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G66" s="18">
         <v>781242</v>
@@ -2333,7 +2333,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2344,10 +2344,10 @@
         <v>10</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F67" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G67" s="18">
         <v>781242</v>
@@ -2356,7 +2356,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2367,10 +2367,10 @@
         <v>10</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F68" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G68" s="18">
         <v>781242</v>
@@ -2379,7 +2379,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2390,10 +2390,10 @@
         <v>10</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F69" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G69" s="18">
         <v>781242</v>
@@ -2402,21 +2402,21 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F70" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G70" s="18">
         <v>781242</v>
@@ -2425,21 +2425,21 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F71" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G71" s="18">
         <v>781242</v>
@@ -2448,21 +2448,21 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F72" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G72" s="18">
         <v>781242</v>
@@ -2471,21 +2471,21 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F73" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G73" s="18">
         <v>781242</v>
@@ -2494,21 +2494,21 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F74" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G74" s="18">
         <v>781242</v>
@@ -2517,21 +2517,21 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="E75" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F75" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G75" s="18">
         <v>781242</v>
@@ -2540,21 +2540,21 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F76" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G76" s="18">
         <v>781242</v>
@@ -2563,21 +2563,21 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F77" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G77" s="18">
         <v>781242</v>
@@ -2586,21 +2586,21 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="E78" s="22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F78" s="24">
-        <v>22916</v>
+        <v>27578</v>
       </c>
       <c r="G78" s="24">
         <v>781242</v>
@@ -2609,7 +2609,7 @@
       <c r="I78" s="25"/>
       <c r="J78" s="26"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="32" t="s">
         <v>76</v>
       </c>
@@ -2620,7 +2620,7 @@
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="32" t="s">
         <v>75</v>
       </c>
